--- a/employee_surveys/029_pc_management_survey--employee_surveys.xlsx
+++ b/employee_surveys/029_pc_management_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>workplace_computers</t>
+          <t>Workplace Computers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>it_support</t>
+          <t>IT Support</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_last_updated</t>
+          <t>Date Last Updated</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>it_support_team</t>
+          <t>IT Support Team</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>issues</t>
+          <t>Issues</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>Date Submitted</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,36 +732,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>Time Submitted</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +778,13 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,13 +801,13 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>employee_id</t>
+          <t>Employee ID</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,13 +824,13 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>supervisor_id</t>
+          <t>Supervisor ID</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,13 +847,13 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,13 +893,13 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>Job Title</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -916,36 +916,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>manager_name</t>
+          <t>Manager Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,18 +957,18 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>issues</t>
+          <t>issues_description</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>issues</t>
+          <t>Issues Description</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -980,18 +980,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>email_description</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Email Description</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1003,18 +1003,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>feedback_description</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Feedback Description</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1026,64 +1026,64 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>department_description</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Department Description</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>time_submitted_description</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>Time Submitted Description</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>submitted_description</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>Submitted Description</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1228,102 +1228,102 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>chatbot</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>chatbot</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>feedback_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chatbot2</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chatbot2</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>chatbot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>chatbot</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>feedback_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>chatbot2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>chatbot2</t>
         </is>
       </c>
     </row>
